--- a/VerveStacks_MYS_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_MYS_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F25FB8-3DE9-4915-9371-EFAAA669E842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7285D54E-673A-49B4-A2C5-A222A4903D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4358,7 +4358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF251C4A-23EA-4095-B4D9-64B2831626C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0242565-38B9-4C8B-A3EB-705190ADC58B}">
   <dimension ref="B3:I176"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_MYS_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_MYS_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7285D54E-673A-49B4-A2C5-A222A4903D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A083AC10-D487-4A38-8A78-D7E4EF4C133E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="657">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -812,6 +812,48 @@
     <t>solar electricity generation in cluster -- 17</t>
   </si>
   <si>
+    <t>elc_spv_MYS_018</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_019</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_020</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_021</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_022</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_023</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_spv_MYS_024</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 24</t>
+  </si>
+  <si>
     <t>elc_wof_MYS_001</t>
   </si>
   <si>
@@ -906,6 +948,30 @@
   </si>
   <si>
     <t>onshore wind electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_007</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_008</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_009</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_won_MYS_010</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 10</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4358,13 +4424,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0242565-38B9-4C8B-A3EB-705190ADC58B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74365624-46AE-46D1-939C-6AFFB114ED05}">
   <dimension ref="B3:I176"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -4398,13 +4464,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="D5" t="s">
         <v>219</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -4413,7 +4479,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I5" t="s">
         <v>224</v>
@@ -4424,13 +4490,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="D6" t="s">
         <v>219</v>
       </c>
       <c r="E6" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -4439,7 +4505,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I6" t="s">
         <v>224</v>
@@ -4450,13 +4516,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D7" t="s">
         <v>219</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -4465,7 +4531,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I7" t="s">
         <v>224</v>
@@ -4476,13 +4542,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="D8" t="s">
         <v>219</v>
       </c>
       <c r="E8" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -4491,7 +4557,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I8" t="s">
         <v>224</v>
@@ -4502,13 +4568,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="D9" t="s">
         <v>219</v>
       </c>
       <c r="E9" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -4517,7 +4583,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I9" t="s">
         <v>224</v>
@@ -4528,13 +4594,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="D10" t="s">
         <v>219</v>
       </c>
       <c r="E10" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -4543,7 +4609,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I10" t="s">
         <v>224</v>
@@ -4554,13 +4620,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
         <v>219</v>
       </c>
       <c r="E11" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -4569,7 +4635,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I11" t="s">
         <v>224</v>
@@ -4580,13 +4646,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="D12" t="s">
         <v>219</v>
       </c>
       <c r="E12" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -4595,7 +4661,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I12" t="s">
         <v>224</v>
@@ -4606,13 +4672,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="D13" t="s">
         <v>219</v>
       </c>
       <c r="E13" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -4621,7 +4687,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I13" t="s">
         <v>224</v>
@@ -4632,13 +4698,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="D14" t="s">
         <v>219</v>
       </c>
       <c r="E14" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -4647,7 +4713,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I14" t="s">
         <v>224</v>
@@ -4658,13 +4724,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="D15" t="s">
         <v>219</v>
       </c>
       <c r="E15" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -4673,7 +4739,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I15" t="s">
         <v>224</v>
@@ -4684,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="D16" t="s">
         <v>219</v>
       </c>
       <c r="E16" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -4699,7 +4765,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I16" t="s">
         <v>224</v>
@@ -4710,13 +4776,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="D17" t="s">
         <v>219</v>
       </c>
       <c r="E17" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -4725,7 +4791,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I17" t="s">
         <v>224</v>
@@ -4736,13 +4802,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="D18" t="s">
         <v>219</v>
       </c>
       <c r="E18" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -4751,7 +4817,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I18" t="s">
         <v>224</v>
@@ -4762,13 +4828,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="D19" t="s">
         <v>219</v>
       </c>
       <c r="E19" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -4777,7 +4843,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I19" t="s">
         <v>224</v>
@@ -4788,13 +4854,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="D20" t="s">
         <v>219</v>
       </c>
       <c r="E20" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -4803,7 +4869,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I20" t="s">
         <v>224</v>
@@ -4814,13 +4880,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="D21" t="s">
         <v>219</v>
       </c>
       <c r="E21" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -4829,7 +4895,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I21" t="s">
         <v>224</v>
@@ -4840,13 +4906,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="D22" t="s">
         <v>219</v>
       </c>
       <c r="E22" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -4855,7 +4921,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I22" t="s">
         <v>224</v>
@@ -4866,13 +4932,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="D23" t="s">
         <v>219</v>
       </c>
       <c r="E23" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -4881,7 +4947,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I23" t="s">
         <v>224</v>
@@ -4892,13 +4958,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="D24" t="s">
         <v>219</v>
       </c>
       <c r="E24" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -4907,7 +4973,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I24" t="s">
         <v>224</v>
@@ -4918,13 +4984,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="D25" t="s">
         <v>219</v>
       </c>
       <c r="E25" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -4933,7 +4999,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I25" t="s">
         <v>224</v>
@@ -4944,13 +5010,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="D26" t="s">
         <v>219</v>
       </c>
       <c r="E26" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -4959,7 +5025,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I26" t="s">
         <v>224</v>
@@ -4970,13 +5036,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="D27" t="s">
         <v>219</v>
       </c>
       <c r="E27" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -4985,7 +5051,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I27" t="s">
         <v>224</v>
@@ -4996,13 +5062,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="D28" t="s">
         <v>219</v>
       </c>
       <c r="E28" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -5011,7 +5077,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I28" t="s">
         <v>224</v>
@@ -5022,13 +5088,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="D29" t="s">
         <v>219</v>
       </c>
       <c r="E29" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -5037,7 +5103,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I29" t="s">
         <v>224</v>
@@ -5048,13 +5114,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="D30" t="s">
         <v>219</v>
       </c>
       <c r="E30" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -5063,7 +5129,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I30" t="s">
         <v>224</v>
@@ -5074,13 +5140,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="D31" t="s">
         <v>219</v>
       </c>
       <c r="E31" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -5089,7 +5155,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I31" t="s">
         <v>224</v>
@@ -5100,13 +5166,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="D32" t="s">
         <v>219</v>
       </c>
       <c r="E32" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -5115,7 +5181,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I32" t="s">
         <v>224</v>
@@ -5126,13 +5192,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="D33" t="s">
         <v>219</v>
       </c>
       <c r="E33" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -5141,7 +5207,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I33" t="s">
         <v>224</v>
@@ -5152,13 +5218,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="D34" t="s">
         <v>219</v>
       </c>
       <c r="E34" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -5167,7 +5233,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I34" t="s">
         <v>224</v>
@@ -5178,13 +5244,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="D35" t="s">
         <v>219</v>
       </c>
       <c r="E35" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -5193,7 +5259,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I35" t="s">
         <v>224</v>
@@ -5204,13 +5270,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="D36" t="s">
         <v>219</v>
       </c>
       <c r="E36" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -5219,7 +5285,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I36" t="s">
         <v>224</v>
@@ -5230,13 +5296,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="D37" t="s">
         <v>219</v>
       </c>
       <c r="E37" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -5245,7 +5311,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I37" t="s">
         <v>224</v>
@@ -5256,13 +5322,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="D38" t="s">
         <v>219</v>
       </c>
       <c r="E38" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -5271,7 +5337,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I38" t="s">
         <v>224</v>
@@ -5282,13 +5348,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="D39" t="s">
         <v>219</v>
       </c>
       <c r="E39" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -5297,7 +5363,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I39" t="s">
         <v>224</v>
@@ -5308,13 +5374,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="D40" t="s">
         <v>219</v>
       </c>
       <c r="E40" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -5323,7 +5389,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I40" t="s">
         <v>224</v>
@@ -5334,13 +5400,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="D41" t="s">
         <v>219</v>
       </c>
       <c r="E41" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -5349,7 +5415,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I41" t="s">
         <v>224</v>
@@ -5360,13 +5426,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="D42" t="s">
         <v>219</v>
       </c>
       <c r="E42" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -5375,7 +5441,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I42" t="s">
         <v>224</v>
@@ -5386,13 +5452,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="D43" t="s">
         <v>219</v>
       </c>
       <c r="E43" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -5401,7 +5467,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I43" t="s">
         <v>224</v>
@@ -5412,13 +5478,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="D44" t="s">
         <v>219</v>
       </c>
       <c r="E44" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -5427,7 +5493,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I44" t="s">
         <v>224</v>
@@ -5438,13 +5504,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="D45" t="s">
         <v>219</v>
       </c>
       <c r="E45" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -5453,7 +5519,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I45" t="s">
         <v>224</v>
@@ -5464,13 +5530,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="D46" t="s">
         <v>219</v>
       </c>
       <c r="E46" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -5479,7 +5545,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I46" t="s">
         <v>224</v>
@@ -5490,13 +5556,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="D47" t="s">
         <v>219</v>
       </c>
       <c r="E47" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -5505,7 +5571,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I47" t="s">
         <v>224</v>
@@ -5516,13 +5582,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="D48" t="s">
         <v>219</v>
       </c>
       <c r="E48" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -5531,7 +5597,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I48" t="s">
         <v>224</v>
@@ -5542,13 +5608,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="D49" t="s">
         <v>219</v>
       </c>
       <c r="E49" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -5557,7 +5623,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I49" t="s">
         <v>224</v>
@@ -5568,13 +5634,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="D50" t="s">
         <v>219</v>
       </c>
       <c r="E50" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -5583,7 +5649,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I50" t="s">
         <v>224</v>
@@ -5594,13 +5660,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="D51" t="s">
         <v>219</v>
       </c>
       <c r="E51" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -5609,7 +5675,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I51" t="s">
         <v>224</v>
@@ -5620,13 +5686,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="D52" t="s">
         <v>219</v>
       </c>
       <c r="E52" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -5635,7 +5701,7 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I52" t="s">
         <v>224</v>
@@ -5646,13 +5712,13 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="D53" t="s">
         <v>219</v>
       </c>
       <c r="E53" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="F53" t="s">
         <v>25</v>
@@ -5661,7 +5727,7 @@
         <v>35</v>
       </c>
       <c r="H53" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I53" t="s">
         <v>224</v>
@@ -5672,13 +5738,13 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="D54" t="s">
         <v>219</v>
       </c>
       <c r="E54" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="F54" t="s">
         <v>25</v>
@@ -5687,7 +5753,7 @@
         <v>35</v>
       </c>
       <c r="H54" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I54" t="s">
         <v>224</v>
@@ -5698,13 +5764,13 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="D55" t="s">
         <v>219</v>
       </c>
       <c r="E55" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="F55" t="s">
         <v>25</v>
@@ -5713,7 +5779,7 @@
         <v>35</v>
       </c>
       <c r="H55" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I55" t="s">
         <v>224</v>
@@ -5724,13 +5790,13 @@
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="D56" t="s">
         <v>219</v>
       </c>
       <c r="E56" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="F56" t="s">
         <v>25</v>
@@ -5739,7 +5805,7 @@
         <v>35</v>
       </c>
       <c r="H56" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I56" t="s">
         <v>224</v>
@@ -5750,13 +5816,13 @@
         <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="D57" t="s">
         <v>219</v>
       </c>
       <c r="E57" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="F57" t="s">
         <v>25</v>
@@ -5765,7 +5831,7 @@
         <v>35</v>
       </c>
       <c r="H57" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I57" t="s">
         <v>224</v>
@@ -5776,13 +5842,13 @@
         <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="D58" t="s">
         <v>219</v>
       </c>
       <c r="E58" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="F58" t="s">
         <v>25</v>
@@ -5791,7 +5857,7 @@
         <v>35</v>
       </c>
       <c r="H58" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I58" t="s">
         <v>224</v>
@@ -5802,13 +5868,13 @@
         <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="D59" t="s">
         <v>219</v>
       </c>
       <c r="E59" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="F59" t="s">
         <v>25</v>
@@ -5817,7 +5883,7 @@
         <v>35</v>
       </c>
       <c r="H59" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I59" t="s">
         <v>224</v>
@@ -5828,13 +5894,13 @@
         <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="D60" t="s">
         <v>219</v>
       </c>
       <c r="E60" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="F60" t="s">
         <v>25</v>
@@ -5843,7 +5909,7 @@
         <v>35</v>
       </c>
       <c r="H60" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I60" t="s">
         <v>224</v>
@@ -5854,13 +5920,13 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="D61" t="s">
         <v>219</v>
       </c>
       <c r="E61" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="F61" t="s">
         <v>25</v>
@@ -5869,7 +5935,7 @@
         <v>35</v>
       </c>
       <c r="H61" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I61" t="s">
         <v>224</v>
@@ -5880,13 +5946,13 @@
         <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="D62" t="s">
         <v>219</v>
       </c>
       <c r="E62" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="F62" t="s">
         <v>25</v>
@@ -5895,7 +5961,7 @@
         <v>35</v>
       </c>
       <c r="H62" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I62" t="s">
         <v>224</v>
@@ -5906,13 +5972,13 @@
         <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="D63" t="s">
         <v>219</v>
       </c>
       <c r="E63" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="F63" t="s">
         <v>25</v>
@@ -5921,7 +5987,7 @@
         <v>35</v>
       </c>
       <c r="H63" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I63" t="s">
         <v>224</v>
@@ -5932,13 +5998,13 @@
         <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="D64" t="s">
         <v>219</v>
       </c>
       <c r="E64" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="F64" t="s">
         <v>25</v>
@@ -5947,7 +6013,7 @@
         <v>35</v>
       </c>
       <c r="H64" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I64" t="s">
         <v>224</v>
@@ -5958,13 +6024,13 @@
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="D65" t="s">
         <v>219</v>
       </c>
       <c r="E65" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="F65" t="s">
         <v>25</v>
@@ -5973,7 +6039,7 @@
         <v>35</v>
       </c>
       <c r="H65" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I65" t="s">
         <v>224</v>
@@ -5984,13 +6050,13 @@
         <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="D66" t="s">
         <v>219</v>
       </c>
       <c r="E66" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="F66" t="s">
         <v>25</v>
@@ -5999,7 +6065,7 @@
         <v>35</v>
       </c>
       <c r="H66" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I66" t="s">
         <v>224</v>
@@ -6010,13 +6076,13 @@
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="D67" t="s">
         <v>219</v>
       </c>
       <c r="E67" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="F67" t="s">
         <v>25</v>
@@ -6025,7 +6091,7 @@
         <v>35</v>
       </c>
       <c r="H67" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I67" t="s">
         <v>224</v>
@@ -6036,13 +6102,13 @@
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="D68" t="s">
         <v>219</v>
       </c>
       <c r="E68" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="F68" t="s">
         <v>25</v>
@@ -6051,7 +6117,7 @@
         <v>35</v>
       </c>
       <c r="H68" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I68" t="s">
         <v>224</v>
@@ -6062,13 +6128,13 @@
         <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="D69" t="s">
         <v>219</v>
       </c>
       <c r="E69" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="F69" t="s">
         <v>25</v>
@@ -6077,7 +6143,7 @@
         <v>35</v>
       </c>
       <c r="H69" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I69" t="s">
         <v>224</v>
@@ -6088,13 +6154,13 @@
         <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="D70" t="s">
         <v>219</v>
       </c>
       <c r="E70" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="F70" t="s">
         <v>25</v>
@@ -6103,7 +6169,7 @@
         <v>35</v>
       </c>
       <c r="H70" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I70" t="s">
         <v>224</v>
@@ -6114,13 +6180,13 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="D71" t="s">
         <v>219</v>
       </c>
       <c r="E71" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="F71" t="s">
         <v>25</v>
@@ -6129,7 +6195,7 @@
         <v>35</v>
       </c>
       <c r="H71" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I71" t="s">
         <v>224</v>
@@ -6140,13 +6206,13 @@
         <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="D72" t="s">
         <v>219</v>
       </c>
       <c r="E72" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="F72" t="s">
         <v>25</v>
@@ -6155,7 +6221,7 @@
         <v>35</v>
       </c>
       <c r="H72" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I72" t="s">
         <v>224</v>
@@ -6166,13 +6232,13 @@
         <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="D73" t="s">
         <v>219</v>
       </c>
       <c r="E73" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="F73" t="s">
         <v>25</v>
@@ -6181,7 +6247,7 @@
         <v>35</v>
       </c>
       <c r="H73" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I73" t="s">
         <v>224</v>
@@ -6192,13 +6258,13 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="D74" t="s">
         <v>219</v>
       </c>
       <c r="E74" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="F74" t="s">
         <v>25</v>
@@ -6207,7 +6273,7 @@
         <v>35</v>
       </c>
       <c r="H74" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I74" t="s">
         <v>224</v>
@@ -6218,13 +6284,13 @@
         <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="D75" t="s">
         <v>219</v>
       </c>
       <c r="E75" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="F75" t="s">
         <v>25</v>
@@ -6233,7 +6299,7 @@
         <v>35</v>
       </c>
       <c r="H75" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I75" t="s">
         <v>224</v>
@@ -6244,13 +6310,13 @@
         <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="D76" t="s">
         <v>219</v>
       </c>
       <c r="E76" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="F76" t="s">
         <v>25</v>
@@ -6259,7 +6325,7 @@
         <v>35</v>
       </c>
       <c r="H76" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I76" t="s">
         <v>224</v>
@@ -6270,13 +6336,13 @@
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="D77" t="s">
         <v>219</v>
       </c>
       <c r="E77" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="F77" t="s">
         <v>25</v>
@@ -6285,7 +6351,7 @@
         <v>35</v>
       </c>
       <c r="H77" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I77" t="s">
         <v>224</v>
@@ -6296,13 +6362,13 @@
         <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="D78" t="s">
         <v>219</v>
       </c>
       <c r="E78" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="F78" t="s">
         <v>25</v>
@@ -6311,7 +6377,7 @@
         <v>35</v>
       </c>
       <c r="H78" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I78" t="s">
         <v>224</v>
@@ -6322,13 +6388,13 @@
         <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="D79" t="s">
         <v>219</v>
       </c>
       <c r="E79" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="F79" t="s">
         <v>25</v>
@@ -6337,7 +6403,7 @@
         <v>35</v>
       </c>
       <c r="H79" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I79" t="s">
         <v>224</v>
@@ -6348,13 +6414,13 @@
         <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="D80" t="s">
         <v>219</v>
       </c>
       <c r="E80" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="F80" t="s">
         <v>25</v>
@@ -6363,7 +6429,7 @@
         <v>35</v>
       </c>
       <c r="H80" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I80" t="s">
         <v>224</v>
@@ -6374,13 +6440,13 @@
         <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="D81" t="s">
         <v>219</v>
       </c>
       <c r="E81" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="F81" t="s">
         <v>25</v>
@@ -6389,7 +6455,7 @@
         <v>35</v>
       </c>
       <c r="H81" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I81" t="s">
         <v>224</v>
@@ -6400,13 +6466,13 @@
         <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="D82" t="s">
         <v>219</v>
       </c>
       <c r="E82" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="F82" t="s">
         <v>25</v>
@@ -6415,7 +6481,7 @@
         <v>35</v>
       </c>
       <c r="H82" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I82" t="s">
         <v>224</v>
@@ -6426,13 +6492,13 @@
         <v>17</v>
       </c>
       <c r="C83" t="s">
-        <v>447</v>
+        <v>469</v>
       </c>
       <c r="D83" t="s">
         <v>219</v>
       </c>
       <c r="E83" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="F83" t="s">
         <v>25</v>
@@ -6441,7 +6507,7 @@
         <v>35</v>
       </c>
       <c r="H83" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I83" t="s">
         <v>224</v>
@@ -6452,13 +6518,13 @@
         <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="D84" t="s">
         <v>219</v>
       </c>
       <c r="E84" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="F84" t="s">
         <v>25</v>
@@ -6467,7 +6533,7 @@
         <v>35</v>
       </c>
       <c r="H84" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I84" t="s">
         <v>224</v>
@@ -6478,13 +6544,13 @@
         <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="D85" t="s">
         <v>219</v>
       </c>
       <c r="E85" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="F85" t="s">
         <v>25</v>
@@ -6493,7 +6559,7 @@
         <v>35</v>
       </c>
       <c r="H85" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I85" t="s">
         <v>224</v>
@@ -6504,13 +6570,13 @@
         <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="D86" t="s">
         <v>219</v>
       </c>
       <c r="E86" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="F86" t="s">
         <v>25</v>
@@ -6519,7 +6585,7 @@
         <v>35</v>
       </c>
       <c r="H86" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I86" t="s">
         <v>224</v>
@@ -6530,13 +6596,13 @@
         <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="D87" t="s">
         <v>219</v>
       </c>
       <c r="E87" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="F87" t="s">
         <v>25</v>
@@ -6545,7 +6611,7 @@
         <v>35</v>
       </c>
       <c r="H87" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I87" t="s">
         <v>224</v>
@@ -6556,13 +6622,13 @@
         <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="D88" t="s">
         <v>219</v>
       </c>
       <c r="E88" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="F88" t="s">
         <v>25</v>
@@ -6571,7 +6637,7 @@
         <v>35</v>
       </c>
       <c r="H88" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I88" t="s">
         <v>224</v>
@@ -6582,13 +6648,13 @@
         <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="D89" t="s">
         <v>219</v>
       </c>
       <c r="E89" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="F89" t="s">
         <v>25</v>
@@ -6597,7 +6663,7 @@
         <v>35</v>
       </c>
       <c r="H89" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I89" t="s">
         <v>224</v>
@@ -6608,13 +6674,13 @@
         <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="D90" t="s">
         <v>219</v>
       </c>
       <c r="E90" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="F90" t="s">
         <v>25</v>
@@ -6623,7 +6689,7 @@
         <v>35</v>
       </c>
       <c r="H90" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I90" t="s">
         <v>224</v>
@@ -6634,13 +6700,13 @@
         <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="D91" t="s">
         <v>219</v>
       </c>
       <c r="E91" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="F91" t="s">
         <v>25</v>
@@ -6649,7 +6715,7 @@
         <v>35</v>
       </c>
       <c r="H91" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I91" t="s">
         <v>224</v>
@@ -6660,13 +6726,13 @@
         <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="D92" t="s">
         <v>219</v>
       </c>
       <c r="E92" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="F92" t="s">
         <v>25</v>
@@ -6675,7 +6741,7 @@
         <v>35</v>
       </c>
       <c r="H92" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I92" t="s">
         <v>224</v>
@@ -6686,13 +6752,13 @@
         <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="D93" t="s">
         <v>219</v>
       </c>
       <c r="E93" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="F93" t="s">
         <v>25</v>
@@ -6701,7 +6767,7 @@
         <v>35</v>
       </c>
       <c r="H93" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I93" t="s">
         <v>224</v>
@@ -6712,13 +6778,13 @@
         <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="D94" t="s">
         <v>219</v>
       </c>
       <c r="E94" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="F94" t="s">
         <v>25</v>
@@ -6727,7 +6793,7 @@
         <v>35</v>
       </c>
       <c r="H94" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I94" t="s">
         <v>224</v>
@@ -6738,13 +6804,13 @@
         <v>17</v>
       </c>
       <c r="C95" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="D95" t="s">
         <v>219</v>
       </c>
       <c r="E95" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="F95" t="s">
         <v>25</v>
@@ -6753,7 +6819,7 @@
         <v>35</v>
       </c>
       <c r="H95" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I95" t="s">
         <v>224</v>
@@ -6764,13 +6830,13 @@
         <v>17</v>
       </c>
       <c r="C96" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="D96" t="s">
         <v>219</v>
       </c>
       <c r="E96" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="F96" t="s">
         <v>25</v>
@@ -6779,7 +6845,7 @@
         <v>35</v>
       </c>
       <c r="H96" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I96" t="s">
         <v>224</v>
@@ -6790,13 +6856,13 @@
         <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="D97" t="s">
         <v>219</v>
       </c>
       <c r="E97" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="F97" t="s">
         <v>25</v>
@@ -6805,7 +6871,7 @@
         <v>35</v>
       </c>
       <c r="H97" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I97" t="s">
         <v>224</v>
@@ -6816,13 +6882,13 @@
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="D98" t="s">
         <v>219</v>
       </c>
       <c r="E98" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="F98" t="s">
         <v>25</v>
@@ -6831,7 +6897,7 @@
         <v>35</v>
       </c>
       <c r="H98" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I98" t="s">
         <v>224</v>
@@ -6842,13 +6908,13 @@
         <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="D99" t="s">
         <v>219</v>
       </c>
       <c r="E99" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="F99" t="s">
         <v>25</v>
@@ -6857,7 +6923,7 @@
         <v>35</v>
       </c>
       <c r="H99" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I99" t="s">
         <v>224</v>
@@ -6868,13 +6934,13 @@
         <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="D100" t="s">
         <v>219</v>
       </c>
       <c r="E100" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="F100" t="s">
         <v>25</v>
@@ -6883,7 +6949,7 @@
         <v>35</v>
       </c>
       <c r="H100" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I100" t="s">
         <v>224</v>
@@ -6894,13 +6960,13 @@
         <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="D101" t="s">
         <v>219</v>
       </c>
       <c r="E101" t="s">
-        <v>484</v>
+        <v>506</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
@@ -6909,7 +6975,7 @@
         <v>35</v>
       </c>
       <c r="H101" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I101" t="s">
         <v>224</v>
@@ -6920,13 +6986,13 @@
         <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="D102" t="s">
         <v>219</v>
       </c>
       <c r="E102" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="F102" t="s">
         <v>25</v>
@@ -6935,7 +7001,7 @@
         <v>35</v>
       </c>
       <c r="H102" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I102" t="s">
         <v>224</v>
@@ -6946,13 +7012,13 @@
         <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="D103" t="s">
         <v>219</v>
       </c>
       <c r="E103" t="s">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="F103" t="s">
         <v>25</v>
@@ -6961,7 +7027,7 @@
         <v>35</v>
       </c>
       <c r="H103" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I103" t="s">
         <v>224</v>
@@ -6972,13 +7038,13 @@
         <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>489</v>
+        <v>511</v>
       </c>
       <c r="D104" t="s">
         <v>219</v>
       </c>
       <c r="E104" t="s">
-        <v>490</v>
+        <v>512</v>
       </c>
       <c r="F104" t="s">
         <v>25</v>
@@ -6987,7 +7053,7 @@
         <v>35</v>
       </c>
       <c r="H104" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I104" t="s">
         <v>224</v>
@@ -6998,13 +7064,13 @@
         <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="D105" t="s">
         <v>219</v>
       </c>
       <c r="E105" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="F105" t="s">
         <v>25</v>
@@ -7013,7 +7079,7 @@
         <v>35</v>
       </c>
       <c r="H105" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I105" t="s">
         <v>224</v>
@@ -7024,13 +7090,13 @@
         <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="D106" t="s">
         <v>219</v>
       </c>
       <c r="E106" t="s">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="F106" t="s">
         <v>25</v>
@@ -7039,7 +7105,7 @@
         <v>35</v>
       </c>
       <c r="H106" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I106" t="s">
         <v>224</v>
@@ -7050,13 +7116,13 @@
         <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="D107" t="s">
         <v>219</v>
       </c>
       <c r="E107" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="F107" t="s">
         <v>25</v>
@@ -7065,7 +7131,7 @@
         <v>35</v>
       </c>
       <c r="H107" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I107" t="s">
         <v>224</v>
@@ -7076,13 +7142,13 @@
         <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="D108" t="s">
         <v>219</v>
       </c>
       <c r="E108" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="F108" t="s">
         <v>25</v>
@@ -7091,7 +7157,7 @@
         <v>35</v>
       </c>
       <c r="H108" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I108" t="s">
         <v>224</v>
@@ -7102,13 +7168,13 @@
         <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>499</v>
+        <v>521</v>
       </c>
       <c r="D109" t="s">
         <v>219</v>
       </c>
       <c r="E109" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="F109" t="s">
         <v>25</v>
@@ -7117,7 +7183,7 @@
         <v>35</v>
       </c>
       <c r="H109" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I109" t="s">
         <v>224</v>
@@ -7128,13 +7194,13 @@
         <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="D110" t="s">
         <v>219</v>
       </c>
       <c r="E110" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="F110" t="s">
         <v>25</v>
@@ -7143,7 +7209,7 @@
         <v>35</v>
       </c>
       <c r="H110" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I110" t="s">
         <v>224</v>
@@ -7154,13 +7220,13 @@
         <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>503</v>
+        <v>525</v>
       </c>
       <c r="D111" t="s">
         <v>219</v>
       </c>
       <c r="E111" t="s">
-        <v>504</v>
+        <v>526</v>
       </c>
       <c r="F111" t="s">
         <v>25</v>
@@ -7169,7 +7235,7 @@
         <v>35</v>
       </c>
       <c r="H111" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I111" t="s">
         <v>224</v>
@@ -7180,13 +7246,13 @@
         <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="D112" t="s">
         <v>219</v>
       </c>
       <c r="E112" t="s">
-        <v>506</v>
+        <v>528</v>
       </c>
       <c r="F112" t="s">
         <v>25</v>
@@ -7195,7 +7261,7 @@
         <v>35</v>
       </c>
       <c r="H112" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I112" t="s">
         <v>224</v>
@@ -7206,13 +7272,13 @@
         <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>507</v>
+        <v>529</v>
       </c>
       <c r="D113" t="s">
         <v>219</v>
       </c>
       <c r="E113" t="s">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="F113" t="s">
         <v>25</v>
@@ -7221,7 +7287,7 @@
         <v>35</v>
       </c>
       <c r="H113" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I113" t="s">
         <v>224</v>
@@ -7232,13 +7298,13 @@
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="D114" t="s">
         <v>219</v>
       </c>
       <c r="E114" t="s">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="F114" t="s">
         <v>25</v>
@@ -7247,7 +7313,7 @@
         <v>35</v>
       </c>
       <c r="H114" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I114" t="s">
         <v>224</v>
@@ -7258,13 +7324,13 @@
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="D115" t="s">
         <v>219</v>
       </c>
       <c r="E115" t="s">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="F115" t="s">
         <v>25</v>
@@ -7273,7 +7339,7 @@
         <v>35</v>
       </c>
       <c r="H115" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I115" t="s">
         <v>224</v>
@@ -7284,13 +7350,13 @@
         <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="D116" t="s">
         <v>219</v>
       </c>
       <c r="E116" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="F116" t="s">
         <v>25</v>
@@ -7299,7 +7365,7 @@
         <v>35</v>
       </c>
       <c r="H116" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I116" t="s">
         <v>224</v>
@@ -7310,13 +7376,13 @@
         <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="D117" t="s">
         <v>219</v>
       </c>
       <c r="E117" t="s">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="F117" t="s">
         <v>25</v>
@@ -7325,7 +7391,7 @@
         <v>35</v>
       </c>
       <c r="H117" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I117" t="s">
         <v>224</v>
@@ -7336,13 +7402,13 @@
         <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="D118" t="s">
         <v>219</v>
       </c>
       <c r="E118" t="s">
-        <v>518</v>
+        <v>540</v>
       </c>
       <c r="F118" t="s">
         <v>25</v>
@@ -7351,7 +7417,7 @@
         <v>35</v>
       </c>
       <c r="H118" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I118" t="s">
         <v>224</v>
@@ -7362,13 +7428,13 @@
         <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="D119" t="s">
         <v>219</v>
       </c>
       <c r="E119" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="F119" t="s">
         <v>25</v>
@@ -7377,7 +7443,7 @@
         <v>35</v>
       </c>
       <c r="H119" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I119" t="s">
         <v>224</v>
@@ -7388,13 +7454,13 @@
         <v>17</v>
       </c>
       <c r="C120" t="s">
-        <v>521</v>
+        <v>543</v>
       </c>
       <c r="D120" t="s">
         <v>219</v>
       </c>
       <c r="E120" t="s">
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="F120" t="s">
         <v>25</v>
@@ -7403,7 +7469,7 @@
         <v>35</v>
       </c>
       <c r="H120" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I120" t="s">
         <v>224</v>
@@ -7414,13 +7480,13 @@
         <v>17</v>
       </c>
       <c r="C121" t="s">
-        <v>523</v>
+        <v>545</v>
       </c>
       <c r="D121" t="s">
         <v>219</v>
       </c>
       <c r="E121" t="s">
-        <v>524</v>
+        <v>546</v>
       </c>
       <c r="F121" t="s">
         <v>25</v>
@@ -7429,7 +7495,7 @@
         <v>35</v>
       </c>
       <c r="H121" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I121" t="s">
         <v>224</v>
@@ -7440,13 +7506,13 @@
         <v>17</v>
       </c>
       <c r="C122" t="s">
-        <v>525</v>
+        <v>547</v>
       </c>
       <c r="D122" t="s">
         <v>219</v>
       </c>
       <c r="E122" t="s">
-        <v>526</v>
+        <v>548</v>
       </c>
       <c r="F122" t="s">
         <v>25</v>
@@ -7455,7 +7521,7 @@
         <v>35</v>
       </c>
       <c r="H122" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I122" t="s">
         <v>224</v>
@@ -7466,13 +7532,13 @@
         <v>17</v>
       </c>
       <c r="C123" t="s">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="D123" t="s">
         <v>219</v>
       </c>
       <c r="E123" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="F123" t="s">
         <v>25</v>
@@ -7481,7 +7547,7 @@
         <v>35</v>
       </c>
       <c r="H123" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I123" t="s">
         <v>224</v>
@@ -7492,13 +7558,13 @@
         <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>529</v>
+        <v>551</v>
       </c>
       <c r="D124" t="s">
         <v>219</v>
       </c>
       <c r="E124" t="s">
-        <v>530</v>
+        <v>552</v>
       </c>
       <c r="F124" t="s">
         <v>25</v>
@@ -7507,7 +7573,7 @@
         <v>35</v>
       </c>
       <c r="H124" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I124" t="s">
         <v>224</v>
@@ -7518,13 +7584,13 @@
         <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>531</v>
+        <v>553</v>
       </c>
       <c r="D125" t="s">
         <v>219</v>
       </c>
       <c r="E125" t="s">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="F125" t="s">
         <v>25</v>
@@ -7533,7 +7599,7 @@
         <v>35</v>
       </c>
       <c r="H125" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I125" t="s">
         <v>224</v>
@@ -7544,13 +7610,13 @@
         <v>17</v>
       </c>
       <c r="C126" t="s">
-        <v>533</v>
+        <v>555</v>
       </c>
       <c r="D126" t="s">
         <v>219</v>
       </c>
       <c r="E126" t="s">
-        <v>534</v>
+        <v>556</v>
       </c>
       <c r="F126" t="s">
         <v>25</v>
@@ -7559,7 +7625,7 @@
         <v>35</v>
       </c>
       <c r="H126" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I126" t="s">
         <v>224</v>
@@ -7570,13 +7636,13 @@
         <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="D127" t="s">
         <v>219</v>
       </c>
       <c r="E127" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="F127" t="s">
         <v>25</v>
@@ -7585,7 +7651,7 @@
         <v>35</v>
       </c>
       <c r="H127" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I127" t="s">
         <v>224</v>
@@ -7596,13 +7662,13 @@
         <v>17</v>
       </c>
       <c r="C128" t="s">
-        <v>537</v>
+        <v>559</v>
       </c>
       <c r="D128" t="s">
         <v>219</v>
       </c>
       <c r="E128" t="s">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="F128" t="s">
         <v>25</v>
@@ -7611,7 +7677,7 @@
         <v>35</v>
       </c>
       <c r="H128" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I128" t="s">
         <v>224</v>
@@ -7622,13 +7688,13 @@
         <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="D129" t="s">
         <v>219</v>
       </c>
       <c r="E129" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
       <c r="F129" t="s">
         <v>25</v>
@@ -7637,7 +7703,7 @@
         <v>35</v>
       </c>
       <c r="H129" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I129" t="s">
         <v>224</v>
@@ -7648,13 +7714,13 @@
         <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="D130" t="s">
         <v>219</v>
       </c>
       <c r="E130" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="F130" t="s">
         <v>25</v>
@@ -7663,7 +7729,7 @@
         <v>35</v>
       </c>
       <c r="H130" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I130" t="s">
         <v>224</v>
@@ -7674,13 +7740,13 @@
         <v>17</v>
       </c>
       <c r="C131" t="s">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="D131" t="s">
         <v>219</v>
       </c>
       <c r="E131" t="s">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="F131" t="s">
         <v>25</v>
@@ -7689,7 +7755,7 @@
         <v>35</v>
       </c>
       <c r="H131" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I131" t="s">
         <v>224</v>
@@ -7700,13 +7766,13 @@
         <v>17</v>
       </c>
       <c r="C132" t="s">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="D132" t="s">
         <v>219</v>
       </c>
       <c r="E132" t="s">
-        <v>546</v>
+        <v>568</v>
       </c>
       <c r="F132" t="s">
         <v>25</v>
@@ -7715,7 +7781,7 @@
         <v>35</v>
       </c>
       <c r="H132" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I132" t="s">
         <v>224</v>
@@ -7726,13 +7792,13 @@
         <v>17</v>
       </c>
       <c r="C133" t="s">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="D133" t="s">
         <v>219</v>
       </c>
       <c r="E133" t="s">
-        <v>548</v>
+        <v>570</v>
       </c>
       <c r="F133" t="s">
         <v>25</v>
@@ -7741,7 +7807,7 @@
         <v>35</v>
       </c>
       <c r="H133" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I133" t="s">
         <v>224</v>
@@ -7752,13 +7818,13 @@
         <v>17</v>
       </c>
       <c r="C134" t="s">
-        <v>549</v>
+        <v>571</v>
       </c>
       <c r="D134" t="s">
         <v>219</v>
       </c>
       <c r="E134" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="F134" t="s">
         <v>25</v>
@@ -7767,7 +7833,7 @@
         <v>35</v>
       </c>
       <c r="H134" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I134" t="s">
         <v>224</v>
@@ -7778,13 +7844,13 @@
         <v>17</v>
       </c>
       <c r="C135" t="s">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="D135" t="s">
         <v>219</v>
       </c>
       <c r="E135" t="s">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="F135" t="s">
         <v>25</v>
@@ -7793,7 +7859,7 @@
         <v>35</v>
       </c>
       <c r="H135" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I135" t="s">
         <v>224</v>
@@ -7804,13 +7870,13 @@
         <v>17</v>
       </c>
       <c r="C136" t="s">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="D136" t="s">
         <v>219</v>
       </c>
       <c r="E136" t="s">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="F136" t="s">
         <v>25</v>
@@ -7819,7 +7885,7 @@
         <v>35</v>
       </c>
       <c r="H136" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I136" t="s">
         <v>224</v>
@@ -7830,13 +7896,13 @@
         <v>17</v>
       </c>
       <c r="C137" t="s">
-        <v>555</v>
+        <v>577</v>
       </c>
       <c r="D137" t="s">
         <v>219</v>
       </c>
       <c r="E137" t="s">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="F137" t="s">
         <v>25</v>
@@ -7845,7 +7911,7 @@
         <v>35</v>
       </c>
       <c r="H137" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I137" t="s">
         <v>224</v>
@@ -7856,13 +7922,13 @@
         <v>17</v>
       </c>
       <c r="C138" t="s">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="D138" t="s">
         <v>219</v>
       </c>
       <c r="E138" t="s">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="F138" t="s">
         <v>25</v>
@@ -7871,7 +7937,7 @@
         <v>35</v>
       </c>
       <c r="H138" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I138" t="s">
         <v>224</v>
@@ -7882,13 +7948,13 @@
         <v>17</v>
       </c>
       <c r="C139" t="s">
-        <v>559</v>
+        <v>581</v>
       </c>
       <c r="D139" t="s">
         <v>219</v>
       </c>
       <c r="E139" t="s">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="F139" t="s">
         <v>25</v>
@@ -7897,7 +7963,7 @@
         <v>35</v>
       </c>
       <c r="H139" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I139" t="s">
         <v>224</v>
@@ -7908,13 +7974,13 @@
         <v>17</v>
       </c>
       <c r="C140" t="s">
-        <v>561</v>
+        <v>583</v>
       </c>
       <c r="D140" t="s">
         <v>219</v>
       </c>
       <c r="E140" t="s">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="F140" t="s">
         <v>25</v>
@@ -7923,7 +7989,7 @@
         <v>35</v>
       </c>
       <c r="H140" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I140" t="s">
         <v>224</v>
@@ -7934,13 +8000,13 @@
         <v>17</v>
       </c>
       <c r="C141" t="s">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="D141" t="s">
         <v>219</v>
       </c>
       <c r="E141" t="s">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="F141" t="s">
         <v>25</v>
@@ -7949,7 +8015,7 @@
         <v>35</v>
       </c>
       <c r="H141" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I141" t="s">
         <v>224</v>
@@ -7960,13 +8026,13 @@
         <v>17</v>
       </c>
       <c r="C142" t="s">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="D142" t="s">
         <v>219</v>
       </c>
       <c r="E142" t="s">
-        <v>566</v>
+        <v>588</v>
       </c>
       <c r="F142" t="s">
         <v>25</v>
@@ -7975,7 +8041,7 @@
         <v>35</v>
       </c>
       <c r="H142" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I142" t="s">
         <v>224</v>
@@ -7986,13 +8052,13 @@
         <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="D143" t="s">
         <v>219</v>
       </c>
       <c r="E143" t="s">
-        <v>568</v>
+        <v>590</v>
       </c>
       <c r="F143" t="s">
         <v>25</v>
@@ -8001,7 +8067,7 @@
         <v>35</v>
       </c>
       <c r="H143" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I143" t="s">
         <v>224</v>
@@ -8012,13 +8078,13 @@
         <v>17</v>
       </c>
       <c r="C144" t="s">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="D144" t="s">
         <v>219</v>
       </c>
       <c r="E144" t="s">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="F144" t="s">
         <v>25</v>
@@ -8027,7 +8093,7 @@
         <v>35</v>
       </c>
       <c r="H144" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I144" t="s">
         <v>224</v>
@@ -8038,13 +8104,13 @@
         <v>17</v>
       </c>
       <c r="C145" t="s">
-        <v>571</v>
+        <v>593</v>
       </c>
       <c r="D145" t="s">
         <v>219</v>
       </c>
       <c r="E145" t="s">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="F145" t="s">
         <v>25</v>
@@ -8053,7 +8119,7 @@
         <v>35</v>
       </c>
       <c r="H145" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I145" t="s">
         <v>224</v>
@@ -8064,13 +8130,13 @@
         <v>17</v>
       </c>
       <c r="C146" t="s">
-        <v>573</v>
+        <v>595</v>
       </c>
       <c r="D146" t="s">
         <v>219</v>
       </c>
       <c r="E146" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="F146" t="s">
         <v>25</v>
@@ -8079,7 +8145,7 @@
         <v>35</v>
       </c>
       <c r="H146" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I146" t="s">
         <v>224</v>
@@ -8090,13 +8156,13 @@
         <v>17</v>
       </c>
       <c r="C147" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="D147" t="s">
         <v>219</v>
       </c>
       <c r="E147" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="F147" t="s">
         <v>25</v>
@@ -8105,7 +8171,7 @@
         <v>35</v>
       </c>
       <c r="H147" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I147" t="s">
         <v>224</v>
@@ -8116,13 +8182,13 @@
         <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>577</v>
+        <v>599</v>
       </c>
       <c r="D148" t="s">
         <v>219</v>
       </c>
       <c r="E148" t="s">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="F148" t="s">
         <v>25</v>
@@ -8131,7 +8197,7 @@
         <v>35</v>
       </c>
       <c r="H148" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I148" t="s">
         <v>224</v>
@@ -8142,13 +8208,13 @@
         <v>17</v>
       </c>
       <c r="C149" t="s">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="D149" t="s">
         <v>219</v>
       </c>
       <c r="E149" t="s">
-        <v>580</v>
+        <v>602</v>
       </c>
       <c r="F149" t="s">
         <v>25</v>
@@ -8157,7 +8223,7 @@
         <v>35</v>
       </c>
       <c r="H149" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I149" t="s">
         <v>224</v>
@@ -8168,13 +8234,13 @@
         <v>17</v>
       </c>
       <c r="C150" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="D150" t="s">
         <v>219</v>
       </c>
       <c r="E150" t="s">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="F150" t="s">
         <v>25</v>
@@ -8183,7 +8249,7 @@
         <v>35</v>
       </c>
       <c r="H150" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I150" t="s">
         <v>224</v>
@@ -8194,13 +8260,13 @@
         <v>17</v>
       </c>
       <c r="C151" t="s">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c r="D151" t="s">
         <v>219</v>
       </c>
       <c r="E151" t="s">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="F151" t="s">
         <v>25</v>
@@ -8209,7 +8275,7 @@
         <v>35</v>
       </c>
       <c r="H151" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I151" t="s">
         <v>224</v>
@@ -8220,13 +8286,13 @@
         <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>585</v>
+        <v>607</v>
       </c>
       <c r="D152" t="s">
         <v>219</v>
       </c>
       <c r="E152" t="s">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="F152" t="s">
         <v>25</v>
@@ -8235,7 +8301,7 @@
         <v>35</v>
       </c>
       <c r="H152" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I152" t="s">
         <v>224</v>
@@ -8246,13 +8312,13 @@
         <v>17</v>
       </c>
       <c r="C153" t="s">
-        <v>587</v>
+        <v>609</v>
       </c>
       <c r="D153" t="s">
         <v>219</v>
       </c>
       <c r="E153" t="s">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c r="F153" t="s">
         <v>25</v>
@@ -8261,7 +8327,7 @@
         <v>35</v>
       </c>
       <c r="H153" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I153" t="s">
         <v>224</v>
@@ -8272,13 +8338,13 @@
         <v>17</v>
       </c>
       <c r="C154" t="s">
-        <v>589</v>
+        <v>611</v>
       </c>
       <c r="D154" t="s">
         <v>219</v>
       </c>
       <c r="E154" t="s">
-        <v>590</v>
+        <v>612</v>
       </c>
       <c r="F154" t="s">
         <v>25</v>
@@ -8287,7 +8353,7 @@
         <v>35</v>
       </c>
       <c r="H154" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I154" t="s">
         <v>224</v>
@@ -8298,13 +8364,13 @@
         <v>17</v>
       </c>
       <c r="C155" t="s">
-        <v>591</v>
+        <v>613</v>
       </c>
       <c r="D155" t="s">
         <v>219</v>
       </c>
       <c r="E155" t="s">
-        <v>592</v>
+        <v>614</v>
       </c>
       <c r="F155" t="s">
         <v>25</v>
@@ -8313,7 +8379,7 @@
         <v>35</v>
       </c>
       <c r="H155" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I155" t="s">
         <v>224</v>
@@ -8324,13 +8390,13 @@
         <v>17</v>
       </c>
       <c r="C156" t="s">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="D156" t="s">
         <v>219</v>
       </c>
       <c r="E156" t="s">
-        <v>594</v>
+        <v>616</v>
       </c>
       <c r="F156" t="s">
         <v>25</v>
@@ -8339,7 +8405,7 @@
         <v>35</v>
       </c>
       <c r="H156" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I156" t="s">
         <v>224</v>
@@ -8350,13 +8416,13 @@
         <v>17</v>
       </c>
       <c r="C157" t="s">
-        <v>595</v>
+        <v>617</v>
       </c>
       <c r="D157" t="s">
         <v>219</v>
       </c>
       <c r="E157" t="s">
-        <v>596</v>
+        <v>618</v>
       </c>
       <c r="F157" t="s">
         <v>25</v>
@@ -8365,7 +8431,7 @@
         <v>35</v>
       </c>
       <c r="H157" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I157" t="s">
         <v>224</v>
@@ -8376,13 +8442,13 @@
         <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>597</v>
+        <v>619</v>
       </c>
       <c r="D158" t="s">
         <v>219</v>
       </c>
       <c r="E158" t="s">
-        <v>598</v>
+        <v>620</v>
       </c>
       <c r="F158" t="s">
         <v>25</v>
@@ -8391,7 +8457,7 @@
         <v>35</v>
       </c>
       <c r="H158" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I158" t="s">
         <v>224</v>
@@ -8402,13 +8468,13 @@
         <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>599</v>
+        <v>621</v>
       </c>
       <c r="D159" t="s">
         <v>219</v>
       </c>
       <c r="E159" t="s">
-        <v>600</v>
+        <v>622</v>
       </c>
       <c r="F159" t="s">
         <v>25</v>
@@ -8417,7 +8483,7 @@
         <v>35</v>
       </c>
       <c r="H159" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I159" t="s">
         <v>224</v>
@@ -8428,13 +8494,13 @@
         <v>17</v>
       </c>
       <c r="C160" t="s">
-        <v>601</v>
+        <v>623</v>
       </c>
       <c r="D160" t="s">
         <v>219</v>
       </c>
       <c r="E160" t="s">
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="F160" t="s">
         <v>25</v>
@@ -8443,7 +8509,7 @@
         <v>35</v>
       </c>
       <c r="H160" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I160" t="s">
         <v>224</v>
@@ -8454,13 +8520,13 @@
         <v>17</v>
       </c>
       <c r="C161" t="s">
-        <v>603</v>
+        <v>625</v>
       </c>
       <c r="D161" t="s">
         <v>219</v>
       </c>
       <c r="E161" t="s">
-        <v>604</v>
+        <v>626</v>
       </c>
       <c r="F161" t="s">
         <v>25</v>
@@ -8469,7 +8535,7 @@
         <v>35</v>
       </c>
       <c r="H161" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I161" t="s">
         <v>224</v>
@@ -8480,13 +8546,13 @@
         <v>17</v>
       </c>
       <c r="C162" t="s">
-        <v>605</v>
+        <v>627</v>
       </c>
       <c r="D162" t="s">
         <v>219</v>
       </c>
       <c r="E162" t="s">
-        <v>606</v>
+        <v>628</v>
       </c>
       <c r="F162" t="s">
         <v>25</v>
@@ -8495,7 +8561,7 @@
         <v>35</v>
       </c>
       <c r="H162" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I162" t="s">
         <v>224</v>
@@ -8506,13 +8572,13 @@
         <v>17</v>
       </c>
       <c r="C163" t="s">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="D163" t="s">
         <v>219</v>
       </c>
       <c r="E163" t="s">
-        <v>608</v>
+        <v>630</v>
       </c>
       <c r="F163" t="s">
         <v>25</v>
@@ -8521,7 +8587,7 @@
         <v>35</v>
       </c>
       <c r="H163" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I163" t="s">
         <v>224</v>
@@ -8532,13 +8598,13 @@
         <v>17</v>
       </c>
       <c r="C164" t="s">
-        <v>609</v>
+        <v>631</v>
       </c>
       <c r="D164" t="s">
         <v>219</v>
       </c>
       <c r="E164" t="s">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="F164" t="s">
         <v>25</v>
@@ -8547,7 +8613,7 @@
         <v>35</v>
       </c>
       <c r="H164" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I164" t="s">
         <v>224</v>
@@ -8558,13 +8624,13 @@
         <v>17</v>
       </c>
       <c r="C165" t="s">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="D165" t="s">
         <v>219</v>
       </c>
       <c r="E165" t="s">
-        <v>612</v>
+        <v>634</v>
       </c>
       <c r="F165" t="s">
         <v>25</v>
@@ -8573,7 +8639,7 @@
         <v>35</v>
       </c>
       <c r="H165" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I165" t="s">
         <v>224</v>
@@ -8584,13 +8650,13 @@
         <v>17</v>
       </c>
       <c r="C166" t="s">
-        <v>613</v>
+        <v>635</v>
       </c>
       <c r="D166" t="s">
         <v>219</v>
       </c>
       <c r="E166" t="s">
-        <v>614</v>
+        <v>636</v>
       </c>
       <c r="F166" t="s">
         <v>25</v>
@@ -8599,7 +8665,7 @@
         <v>35</v>
       </c>
       <c r="H166" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I166" t="s">
         <v>224</v>
@@ -8610,13 +8676,13 @@
         <v>17</v>
       </c>
       <c r="C167" t="s">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="D167" t="s">
         <v>219</v>
       </c>
       <c r="E167" t="s">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="F167" t="s">
         <v>25</v>
@@ -8625,7 +8691,7 @@
         <v>35</v>
       </c>
       <c r="H167" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I167" t="s">
         <v>224</v>
@@ -8636,13 +8702,13 @@
         <v>17</v>
       </c>
       <c r="C168" t="s">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="D168" t="s">
         <v>219</v>
       </c>
       <c r="E168" t="s">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="F168" t="s">
         <v>25</v>
@@ -8651,7 +8717,7 @@
         <v>35</v>
       </c>
       <c r="H168" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I168" t="s">
         <v>224</v>
@@ -8662,13 +8728,13 @@
         <v>17</v>
       </c>
       <c r="C169" t="s">
-        <v>619</v>
+        <v>641</v>
       </c>
       <c r="D169" t="s">
         <v>219</v>
       </c>
       <c r="E169" t="s">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="F169" t="s">
         <v>25</v>
@@ -8677,7 +8743,7 @@
         <v>35</v>
       </c>
       <c r="H169" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I169" t="s">
         <v>224</v>
@@ -8688,13 +8754,13 @@
         <v>17</v>
       </c>
       <c r="C170" t="s">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="D170" t="s">
         <v>219</v>
       </c>
       <c r="E170" t="s">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="F170" t="s">
         <v>25</v>
@@ -8703,7 +8769,7 @@
         <v>35</v>
       </c>
       <c r="H170" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I170" t="s">
         <v>224</v>
@@ -8714,13 +8780,13 @@
         <v>17</v>
       </c>
       <c r="C171" t="s">
-        <v>623</v>
+        <v>645</v>
       </c>
       <c r="D171" t="s">
         <v>219</v>
       </c>
       <c r="E171" t="s">
-        <v>624</v>
+        <v>646</v>
       </c>
       <c r="F171" t="s">
         <v>25</v>
@@ -8729,7 +8795,7 @@
         <v>35</v>
       </c>
       <c r="H171" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I171" t="s">
         <v>224</v>
@@ -8740,13 +8806,13 @@
         <v>17</v>
       </c>
       <c r="C172" t="s">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="D172" t="s">
         <v>219</v>
       </c>
       <c r="E172" t="s">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="F172" t="s">
         <v>25</v>
@@ -8755,7 +8821,7 @@
         <v>35</v>
       </c>
       <c r="H172" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I172" t="s">
         <v>224</v>
@@ -8766,13 +8832,13 @@
         <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>627</v>
+        <v>649</v>
       </c>
       <c r="D173" t="s">
         <v>219</v>
       </c>
       <c r="E173" t="s">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="F173" t="s">
         <v>25</v>
@@ -8781,7 +8847,7 @@
         <v>35</v>
       </c>
       <c r="H173" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I173" t="s">
         <v>224</v>
@@ -8792,13 +8858,13 @@
         <v>17</v>
       </c>
       <c r="C174" t="s">
-        <v>629</v>
+        <v>651</v>
       </c>
       <c r="D174" t="s">
         <v>219</v>
       </c>
       <c r="E174" t="s">
-        <v>630</v>
+        <v>652</v>
       </c>
       <c r="F174" t="s">
         <v>25</v>
@@ -8807,7 +8873,7 @@
         <v>35</v>
       </c>
       <c r="H174" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I174" t="s">
         <v>224</v>
@@ -8818,13 +8884,13 @@
         <v>17</v>
       </c>
       <c r="C175" t="s">
-        <v>631</v>
+        <v>653</v>
       </c>
       <c r="D175" t="s">
         <v>219</v>
       </c>
       <c r="E175" t="s">
-        <v>632</v>
+        <v>654</v>
       </c>
       <c r="F175" t="s">
         <v>25</v>
@@ -8833,7 +8899,7 @@
         <v>35</v>
       </c>
       <c r="H175" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I175" t="s">
         <v>224</v>
@@ -8844,13 +8910,13 @@
         <v>17</v>
       </c>
       <c r="C176" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="D176" t="s">
         <v>219</v>
       </c>
       <c r="E176" t="s">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="F176" t="s">
         <v>25</v>
@@ -8859,7 +8925,7 @@
         <v>35</v>
       </c>
       <c r="H176" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I176" t="s">
         <v>224</v>
@@ -8872,7 +8938,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S37"/>
+  <dimension ref="B3:S48"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -9952,6 +10018,259 @@
         <v>35</v>
       </c>
       <c r="S37" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="13:19">
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>289</v>
+      </c>
+      <c r="O38" t="s">
+        <v>219</v>
+      </c>
+      <c r="P38" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>25</v>
+      </c>
+      <c r="R38" t="s">
+        <v>35</v>
+      </c>
+      <c r="S38" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="13:19">
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>291</v>
+      </c>
+      <c r="O39" t="s">
+        <v>219</v>
+      </c>
+      <c r="P39" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>25</v>
+      </c>
+      <c r="R39" t="s">
+        <v>35</v>
+      </c>
+      <c r="S39" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="13:19">
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>293</v>
+      </c>
+      <c r="O40" t="s">
+        <v>219</v>
+      </c>
+      <c r="P40" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>25</v>
+      </c>
+      <c r="R40" t="s">
+        <v>35</v>
+      </c>
+      <c r="S40" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="13:19">
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>295</v>
+      </c>
+      <c r="O41" t="s">
+        <v>219</v>
+      </c>
+      <c r="P41" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>25</v>
+      </c>
+      <c r="R41" t="s">
+        <v>35</v>
+      </c>
+      <c r="S41" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="13:19">
+      <c r="M42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>297</v>
+      </c>
+      <c r="O42" t="s">
+        <v>219</v>
+      </c>
+      <c r="P42" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>25</v>
+      </c>
+      <c r="R42" t="s">
+        <v>35</v>
+      </c>
+      <c r="S42" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="13:19">
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>299</v>
+      </c>
+      <c r="O43" t="s">
+        <v>219</v>
+      </c>
+      <c r="P43" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>25</v>
+      </c>
+      <c r="R43" t="s">
+        <v>35</v>
+      </c>
+      <c r="S43" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="13:19">
+      <c r="M44" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>301</v>
+      </c>
+      <c r="O44" t="s">
+        <v>219</v>
+      </c>
+      <c r="P44" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>25</v>
+      </c>
+      <c r="R44" t="s">
+        <v>35</v>
+      </c>
+      <c r="S44" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" spans="13:19">
+      <c r="M45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>303</v>
+      </c>
+      <c r="O45" t="s">
+        <v>219</v>
+      </c>
+      <c r="P45" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>25</v>
+      </c>
+      <c r="R45" t="s">
+        <v>35</v>
+      </c>
+      <c r="S45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="13:19">
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>305</v>
+      </c>
+      <c r="O46" t="s">
+        <v>219</v>
+      </c>
+      <c r="P46" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>25</v>
+      </c>
+      <c r="R46" t="s">
+        <v>35</v>
+      </c>
+      <c r="S46" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47" spans="13:19">
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>307</v>
+      </c>
+      <c r="O47" t="s">
+        <v>219</v>
+      </c>
+      <c r="P47" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>25</v>
+      </c>
+      <c r="R47" t="s">
+        <v>35</v>
+      </c>
+      <c r="S47" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="13:19">
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>309</v>
+      </c>
+      <c r="O48" t="s">
+        <v>219</v>
+      </c>
+      <c r="P48" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>25</v>
+      </c>
+      <c r="R48" t="s">
+        <v>35</v>
+      </c>
+      <c r="S48" t="s">
         <v>224</v>
       </c>
     </row>
